--- a/СВО на 01.10.2026.xlsx
+++ b/СВО на 01.10.2026.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">предыдущий период</t>
   </si>
   <si>
-    <t xml:space="preserve">За 4 недели</t>
+    <t xml:space="preserve">За 3 недели</t>
   </si>
   <si>
     <t xml:space="preserve">Всего трудоустройство</t>
@@ -222,13 +222,13 @@
     <t xml:space="preserve"> На 13.08.2026</t>
   </si>
   <si>
+    <t xml:space="preserve">За 4 недели</t>
+  </si>
+  <si>
     <t xml:space="preserve"> На 15.07.2026</t>
   </si>
   <si>
     <t xml:space="preserve">предыдущая неделя</t>
-  </si>
-  <si>
-    <t xml:space="preserve">За 3 недели</t>
   </si>
   <si>
     <t xml:space="preserve">9 Нац проект</t>
@@ -3639,7 +3639,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -3648,7 +3648,7 @@
         <v>53</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -3657,7 +3657,7 @@
         <v>53</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -3666,7 +3666,7 @@
         <v>53</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -6258,7 +6258,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -6267,7 +6267,7 @@
         <v>55</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -6276,7 +6276,7 @@
         <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -6285,7 +6285,7 @@
         <v>70</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -8874,7 +8874,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -8883,7 +8883,7 @@
         <v>69</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -8892,7 +8892,7 @@
         <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -8901,7 +8901,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -11493,7 +11493,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -11502,7 +11502,7 @@
         <v>69</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -11511,7 +11511,7 @@
         <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -11520,7 +11520,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -14086,7 +14086,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -14095,7 +14095,7 @@
         <v>69</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -14104,7 +14104,7 @@
         <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -14113,7 +14113,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -22044,7 +22044,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>14</v>
@@ -22053,7 +22053,7 @@
         <v>7</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>14</v>
@@ -22062,7 +22062,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>14</v>
@@ -22071,7 +22071,7 @@
         <v>17</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="O3" s="16" t="s">
         <v>18</v>
@@ -24615,7 +24615,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -24705,40 +24705,40 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="O3" s="16" t="s">
         <v>18</v>
@@ -27345,7 +27345,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -27354,7 +27354,7 @@
         <v>55</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -27363,7 +27363,7 @@
         <v>55</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -27372,7 +27372,7 @@
         <v>55</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -29979,7 +29979,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -29988,7 +29988,7 @@
         <v>55</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -29997,7 +29997,7 @@
         <v>55</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -30006,7 +30006,7 @@
         <v>55</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -32615,7 +32615,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -32624,7 +32624,7 @@
         <v>53</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -32633,7 +32633,7 @@
         <v>53</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -32642,7 +32642,7 @@
         <v>53</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
@@ -35247,7 +35247,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>7</v>
@@ -35256,7 +35256,7 @@
         <v>53</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>7</v>
@@ -35265,7 +35265,7 @@
         <v>53</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>16</v>
@@ -35274,7 +35274,7 @@
         <v>53</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>17</v>
